--- a/Trắc nghiệm ôn luyện/Tester Technical/multiple_choice_sample_template_DB_PERF_TESTING.xlsx
+++ b/Trắc nghiệm ôn luyện/Tester Technical/multiple_choice_sample_template_DB_PERF_TESTING.xlsx
@@ -453,19 +453,19 @@
         <v>Kiểm thử hiệu năng là kiểm thử phi chức năng, đánh giá các đặc tính tốc độ, độ ổn định và tài nguyên hệ thống tiêu thụ dưới các mức tải khác nhau.</v>
       </c>
       <c r="E2" t="str">
-        <v>Đánh giá tốc độ phản hồi, độ ổn định, độ tin cậy và khả năng mở rộng của hệ thống dưới các điều kiện tải khác nhau — đánh giá vận hành dưới tải</v>
+        <v>Kiểm tra xem các thuật toán mã hóa mật khẩu của hệ thống có bị bẻ khóa hay không — kiểm thử bảo mật mật khẩu</v>
       </c>
       <c r="F2" t="str">
         <v>Tìm kiếm các lỗi viết sai chính tả hoặc sai lệch màu sắc hiển thị trên giao diện — kiểm tra giao diện và chính tả</v>
       </c>
       <c r="G2" t="str">
-        <v>Kiểm tra xem các thuật toán mã hóa mật khẩu của hệ thống có bị bẻ khóa hay không — kiểm thử bảo mật mật khẩu</v>
+        <v>Đánh giá tốc độ phản hồi, độ ổn định, độ tin cậy và khả năng mở rộng của hệ thống dưới các điều kiện tải khác nhau — đánh giá vận hành dưới tải</v>
       </c>
       <c r="H2" t="str">
         <v>Xây dựng các kịch bản kiểm thử tự động cho luồng đăng ký tài khoản — kiểm thử tự động chức năng</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -485,13 +485,13 @@
         <v>Khoảng thời gian kể từ khi người dùng gửi yêu cầu (Request) cho đến khi nhận được phản hồi (Response) hoàn chỉnh từ hệ thống — thời gian gửi nhận yêu cầu phản hồi</v>
       </c>
       <c r="F3" t="str">
+        <v>Tổng thời gian chạy toàn bộ bộ kịch bản kiểm thử tự động của dự án — thời gian chạy test suite</v>
+      </c>
+      <c r="G3" t="str">
         <v>Thời gian lập trình viên cần để sửa xong một lỗi nghiêm trọng trong mã nguồn — thời gian sửa lỗi của dev</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>Số giây tối đa trình duyệt web hiển thị màn hình trống trước khi bắt đầu tải trang — thời gian tải trang trống</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Tổng thời gian chạy toàn bộ bộ kịch bản kiểm thử tự động của dự án — thời gian chạy test suite</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -511,19 +511,19 @@
         <v>Throughput (thông lượng) thể hiện năng lực tải của hệ thống. Thông lượng cao và ổn định chứng tỏ hệ thống xử lý song song tốt.</v>
       </c>
       <c r="E4" t="str">
+        <v>Kích thước dung lượng file cài đặt của ứng dụng di động trên bộ nhớ máy — dung lượng file cài</v>
+      </c>
+      <c r="F4" t="str">
         <v>Số lượng yêu cầu (Requests) hoặc lượng dữ liệu hệ thống có thể xử lý thành công trong một đơn vị thời gian (ví dụ: requests/giây) — băng thông xử lý yêu cầu</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>Tổng số lỗi bảo mật được quét và phát hiện thành công trong mã nguồn — số lượng lỗi bảo mật</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>Số lượng test case tối đa một tester có thể chạy thủ công trong một ngày — năng suất chạy test tay</v>
       </c>
-      <c r="H4" t="str">
-        <v>Kích thước dung lượng file cài đặt của ứng dụng di động trên bộ nhớ máy — dung lượng file cài</v>
-      </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -540,19 +540,19 @@
         <v>Thread Group trong JMeter đại diện cho nhóm người dùng ảo. Cấu hình số Threads chính là cấu hình số Virtual Users (VUs) tham gia tải.</v>
       </c>
       <c r="E5" t="str">
+        <v>Địa chỉ URL và phương thức gọi API (GET, POST) cần kiểm thử — cấu hình endpoint API</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Các câu lệnh truy vấn dữ liệu SQL cần chạy trong cơ sở dữ liệu — cấu hình truy vấn database</v>
+      </c>
+      <c r="G5" t="str">
         <v>Số lượng người dùng giả lập (Virtual Users), thời gian tăng tải (Ramp-up period) và số vòng lặp chạy test — cấu hình người dùng giả lập</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Địa chỉ URL và phương thức gọi API (GET, POST) cần kiểm thử — cấu hình endpoint API</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Các câu lệnh truy vấn dữ liệu SQL cần chạy trong cơ sở dữ liệu — cấu hình truy vấn database</v>
       </c>
       <c r="H5" t="str">
         <v>Biểu đồ trực quan hiển thị kết quả thời gian phản hồi dưới dạng đồ thị — cấu hình biểu đồ hiển thị</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -569,19 +569,19 @@
         <v>Hàm `COUNT(*)` trong SQL dùng để đếm số lượng dòng thỏa mãn điều kiện trong bảng dữ liệu.</v>
       </c>
       <c r="E6" t="str">
-        <v>SELECT COUNT(*) FROM table_name; — câu lệnh đếm tổng bản ghi</v>
+        <v>SELECT MAX(*) FROM table_name; — câu lệnh tìm giá trị lớn nhất</v>
       </c>
       <c r="F6" t="str">
         <v>SELECT SUM(*) FROM table_name; — câu lệnh tính tổng giá trị số</v>
       </c>
       <c r="G6" t="str">
-        <v>SELECT MAX(*) FROM table_name; — câu lệnh tìm giá trị lớn nhất</v>
+        <v>SELECT LIMIT(*) FROM table_name; — câu lệnh giới hạn dòng trả về</v>
       </c>
       <c r="H6" t="str">
-        <v>SELECT LIMIT(*) FROM table_name; — câu lệnh giới hạn dòng trả về</v>
+        <v>SELECT COUNT(*) FROM table_name; — câu lệnh đếm tổng bản ghi</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -598,19 +598,19 @@
         <v>Để đảm bảo tính độc lập và không làm bẩn dữ liệu môi trường test, sau khi chạy các test case thực hiện ghi dữ liệu (INSERT/UPDATE/DELETE), QA gọi `ROLLBACK` để hoàn tác giao dịch.</v>
       </c>
       <c r="E7" t="str">
+        <v>Tự động sao lưu dữ liệu của bảng sang một máy chủ dự phòng khác — sao lưu dự phòng</v>
+      </c>
+      <c r="F7" t="str">
         <v>Hủy bỏ các thay đổi dữ liệu vừa thực hiện trong giao dịch (Transaction) để trả database về trạng thái sạch ban đầu — rollback trả về trạng thái cũ</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
+        <v>Mã hóa các mật khẩu của tài khoản vừa được tạo trong bảng người dùng — mã hóa mật khẩu</v>
+      </c>
+      <c r="H7" t="str">
         <v>Xác nhận và lưu vĩnh viễn các thay đổi dữ liệu đó vào trong ổ cứng máy chủ — commit lưu dữ liệu</v>
       </c>
-      <c r="G7" t="str">
-        <v>Tự động sao lưu dữ liệu của bảng sang một máy chủ dự phòng khác — sao lưu dự phòng</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Mã hóa các mật khẩu của tài khoản vừa được tạo trong bảng người dùng — mã hóa mật khẩu</v>
-      </c>
       <c r="I7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -630,13 +630,13 @@
         <v>Thu thập, phân tích và hiển thị kết quả kiểm thử hiệu năng dưới dạng bảng biểu hoặc đồ thị trực quan — thu thập hiển thị kết quả</v>
       </c>
       <c r="F8" t="str">
+        <v>Chèn các tham số dữ liệu ngẫu nhiên vào trong thân của request gửi đi — chèn tham số dữ liệu</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Tự động tắt trình duyệt web khi phát sinh lỗi quá tải trên máy chủ — tắt trình duyệt</v>
+      </c>
+      <c r="H8" t="str">
         <v>Gửi các request HTTP lên máy chủ để giả lập tải người dùng — giả lập tải gửi request</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Chèn các tham số dữ liệu ngẫu nhiên vào trong thân của request gửi đi — chèn tham số dữ liệu</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Tự động tắt trình duyệt web khi phát sinh lỗi quá tải trên máy chủ — tắt trình duyệt</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -656,19 +656,19 @@
         <v>Từ khóa `DISTINCT` đi sau SELECT dùng để loại bỏ các dòng trùng lặp trong tập kết quả trả về của truy vấn.</v>
       </c>
       <c r="E9" t="str">
-        <v>DISTINCT — ví dụ `SELECT DISTINCT category` lấy các danh mục độc nhất — lọc trùng DISTINCT</v>
+        <v>ORDER BY — sắp xếp thứ tự hiển thị của các dòng dữ liệu trả về — sắp xếp ORDER BY</v>
       </c>
       <c r="F9" t="str">
         <v>UNIQUE — ràng buộc tính duy nhất của cột khi tạo bảng — ràng buộc UNIQUE</v>
       </c>
       <c r="G9" t="str">
+        <v>DISTINCT — ví dụ `SELECT DISTINCT category` lấy các danh mục độc nhất — lọc trùng DISTINCT</v>
+      </c>
+      <c r="H9" t="str">
         <v>GROUP BY — gom nhóm các hàng có cùng giá trị để thực hiện hàm tổng hợp — gom nhóm GROUP BY</v>
       </c>
-      <c r="H9" t="str">
-        <v>ORDER BY — sắp xếp thứ tự hiển thị của các dòng dữ liệu trả về — sắp xếp ORDER BY</v>
-      </c>
       <c r="I9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -685,19 +685,19 @@
         <v>Latency (độ trễ mạng) đo lường thời gian gói tin đi trên đường truyền. Response Time = Latency (request) + Server Processing Time + Latency (response) + Client Rendering (nếu có).</v>
       </c>
       <c r="E10" t="str">
+        <v>Latency đo lường bằng số lượng pixels hiển thị; còn Response Time đo lường bằng giây — đơn vị đo lường</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Latency luôn luôn có giá trị lớn gấp đôi so với Response Time trong mọi điều kiện mạng — so sánh quy mô giá trị</v>
+      </c>
+      <c r="G10" t="str">
         <v>Latency là thời gian truyền gói tin từ client đến server; Response Time bao gồm cả Latency và thời gian server xử lý yêu cầu đó — thời gian truyền dẫn mạng vs tổng thời gian xử lý</v>
       </c>
-      <c r="F10" t="str">
+      <c r="H10" t="str">
         <v>Latency chỉ áp dụng cho kiểm thử tự động; còn Response Time chỉ áp dụng cho kiểm thử thủ công — phân loại phương pháp test</v>
       </c>
-      <c r="G10" t="str">
-        <v>Latency đo lường bằng số lượng pixels hiển thị; còn Response Time đo lường bằng giây — đơn vị đo lường</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Latency luôn luôn có giá trị lớn gấp đôi so với Response Time trong mọi điều kiện mạng — so sánh quy mô giá trị</v>
-      </c>
       <c r="I10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -717,13 +717,13 @@
         <v>Duy trì tải lượng người dùng dự kiến trong một khoảng thời gian dài (24-72 giờ) để phát hiện các lỗi rò rỉ bộ nhớ (Memory Leaks) hoặc đầy ổ cứng log — kiểm thử độ bền phát hiện rò rỉ</v>
       </c>
       <c r="F11" t="str">
+        <v>Đo lường thời gian cần thiết để khôi phục hệ thống máy chủ sau khi bị cháy nổ — phục vụ diễn tập cháy nổ</v>
+      </c>
+      <c r="G11" t="str">
         <v>Tăng tải đột biến lên gấp 10 lần trong vòng 5 giây rồi ngắt tải ngay lập tức — kiểm thử đột biến tải</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>Kiểm tra khả năng chịu va đập vật lý của các thiết bị điện thoại di động thông minh — kiểm tra độ bền điện thoại</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Đo lường thời gian cần thiết để khôi phục hệ thống máy chủ sau khi bị cháy nổ — phục vụ diễn tập cháy nổ</v>
       </c>
       <c r="I11">
         <v>1</v>
@@ -743,19 +743,19 @@
         <v>WHERE lọc các dòng thô ở tầng vật lý (giảm số lượng dòng đưa vào xử lý). HAVING lọc trên tập kết quả đã được GROUP BY và tính toán hàm tổng hợp (như SUM, AVG), do đó sử dụng HAVING sai cách trên bảng lớn sẽ gây chậm truy vấn.</v>
       </c>
       <c r="E12" t="str">
-        <v>WHERE lọc dữ liệu trước khi thực hiện gom nhóm (GROUP BY) và chạy nhanh hơn; HAVING chỉ lọc dữ liệu sau khi đã gom nhóm xong các hàm tổng hợp — lọc trước khi nhóm vs lọc sau khi nhóm</v>
+        <v>WHERE do QA tự viết; còn HAVING do lập trình viên tự động chèn vào code — phân chia vai trò viết câu lệnh</v>
       </c>
       <c r="F12" t="str">
         <v>WHERE chỉ dùng cho kiểu dữ liệu số; còn HAVING chỉ dùng cho kiểu dữ liệu chuỗi văn bản — kiểu dữ liệu lọc</v>
       </c>
       <c r="G12" t="str">
-        <v>WHERE do QA tự viết; còn HAVING do lập trình viên tự động chèn vào code — phân chia vai trò viết câu lệnh</v>
+        <v>WHERE lọc dữ liệu trước khi thực hiện gom nhóm (GROUP BY) và chạy nhanh hơn; HAVING chỉ lọc dữ liệu sau khi đã gom nhóm xong các hàm tổng hợp — lọc trước khi nhóm vs lọc sau khi nhóm</v>
       </c>
       <c r="H12" t="str">
         <v>WHERE bắt buộc phải đi kèm với từ khóa ORDER BY; còn HAVING đi kèm với DISTINCT — liên kết từ khóa</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -775,13 +775,13 @@
         <v>Vì chế độ GUI tiêu tốn rất nhiều tài nguyên CPU/RAM của máy chạy test để vẽ biểu đồ thời gian thực, dẫn đến kết quả đo lường tải bị sai lệch hoặc sập tool — chế độ Non-GUI tiết kiệm tài nguyên máy chạy test</v>
       </c>
       <c r="F13" t="str">
+        <v>Vì chế độ GUI chỉ hỗ trợ chạy tối đa 10 người dùng ảo trong toàn bộ phiên chạy — giới hạn người dùng GUI</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Vì chế độ Non-GUI bắt buộc phải có chứng chỉ kỹ sư mạng Cisco mới vận hành được — yêu cầu chứng chỉ mạng</v>
+      </c>
+      <c r="H13" t="str">
         <v>Vì chế độ Non-GUI tự động mã hóa toàn bộ dữ liệu báo cáo gửi đi bằng giao thức bảo mật HTTPS — bảo mật báo cáo</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Vì chế độ GUI chỉ hỗ trợ chạy tối đa 10 người dùng ảo trong toàn bộ phiên chạy — giới hạn người dùng GUI</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Vì chế độ Non-GUI bắt buộc phải có chứng chỉ kỹ sư mạng Cisco mới vận hành được — yêu cầu chứng chỉ mạng</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -801,10 +801,10 @@
         <v>UNION thực hiện thêm một bước lọc trùng (sorting and filtering) ngầm nên tiêu tốn tài nguyên CPU của database hơn. Nếu nghiệp vụ chắc chắn không có trùng lặp hoặc chấp nhận trùng lặp, nên dùng `UNION ALL` để tối ưu hiệu năng.</v>
       </c>
       <c r="E14" t="str">
+        <v>UNION chỉ ghép các cột theo chiều dọc; còn UNION ALL ghép các cột theo chiều ngang — hướng ghép bảng</v>
+      </c>
+      <c r="F14" t="str">
         <v>UNION gộp kết quả và tự động loại bỏ các dòng trùng lặp (chạy chậm hơn do phải lọc); UNION ALL gộp toàn bộ bao gồm cả dòng trùng lặp (chạy nhanh hơn) — loại bỏ trùng lặp vs gộp toàn bộ</v>
-      </c>
-      <c r="F14" t="str">
-        <v>UNION chỉ ghép các cột theo chiều dọc; còn UNION ALL ghép các cột theo chiều ngang — hướng ghép bảng</v>
       </c>
       <c r="G14" t="str">
         <v>UNION chỉ chạy trên hệ quản trị MySQL; còn UNION ALL chỉ chạy trên Microsoft SQL Server — hệ quản trị cơ sở dữ liệu hỗ trợ</v>
@@ -813,7 +813,7 @@
         <v>UNION bắt buộc phải có tối thiểu 3 bảng dữ liệu tham gia liên kết — số lượng bảng tối thiểu</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -833,13 +833,13 @@
         <v>Atomicity (Tính nguyên tố), Consistency (Tính nhất quán), Isolation (Tính cô lập), Durability (Tính bền vững) — tiêu chuẩn giao dịch ACID</v>
       </c>
       <c r="F15" t="str">
+        <v>Authentication, Cryptography, Integrity, Decryption — quy chuẩn bảo mật dữ liệu</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Aggregation, Collection, Indexing, De-duplication — quy trình xử lý dữ liệu lớn</v>
+      </c>
+      <c r="H15" t="str">
         <v>Accuracy, Compatibility, Integration, Development — quy chuẩn chất lượng phần mềm</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Authentication, Cryptography, Integrity, Decryption — quy chuẩn bảo mật dữ liệu</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Aggregation, Collection, Indexing, De-duplication — quy trình xử lý dữ liệu lớn</v>
       </c>
       <c r="I15">
         <v>1</v>
@@ -859,19 +859,19 @@
         <v>Nếu không có Assertion, JMeter chỉ kiểm tra lỗi ở tầng mạng (ví dụ kết nối được là đánh dấu Pass). Nhưng máy chủ có thể trả về trang lỗi 500 kèm nội dung "Database Error" dạng HTML. Dùng Response Assertion để kiểm tra sự hiện diện của text đúng hoặc status code 200.</v>
       </c>
       <c r="E16" t="str">
-        <v>Kiểm tra dữ liệu phản hồi (Status Code, Text trong body) của máy chủ trả về có đúng kỳ vọng không, nếu sai sẽ đánh dấu request đó bị lỗi (Fail) — xác thực phản hồi máy chủ</v>
+        <v>Mã hóa toàn bộ nội dung của các file báo cáo kết quả chạy test sang định dạng PDF — định dạng báo cáo</v>
       </c>
       <c r="F16" t="str">
         <v>Tự động điều chỉnh tần suất gửi yêu cầu API của người dùng ảo tăng lên gấp đôi — tăng tần suất gửi</v>
       </c>
       <c r="G16" t="str">
-        <v>Mã hóa toàn bộ nội dung của các file báo cáo kết quả chạy test sang định dạng PDF — định dạng báo cáo</v>
+        <v>Kiểm tra dữ liệu phản hồi (Status Code, Text trong body) của máy chủ trả về có đúng kỳ vọng không, nếu sai sẽ đánh dấu request đó bị lỗi (Fail) — xác thực phản hồi máy chủ</v>
       </c>
       <c r="H16" t="str">
         <v>Tự động chèn các mã số định danh ID ngẫu nhiên vào database khi nhận được request — chèn dữ liệu ID</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -888,19 +888,19 @@
         <v>Index giống như mục lục của cuốn sách. Tra cứu từ khóa trong mục lục giúp lật nhanh đến trang cần tìm (quét chỉ mục nhanh hơn quét toàn bảng Table Scan). Tuy nhiên, mỗi khi thêm/sửa/xóa dòng, database phải cập nhật lại mục lục này nên làm chậm tốc độ ghi.</v>
       </c>
       <c r="E17" t="str">
-        <v>Giúp tăng tốc độ truy vấn đọc dữ liệu (SELECT) cực nhanh; nhưng làm chậm tốc độ ghi dữ liệu (INSERT/UPDATE/DELETE) và tiêu tốn dung lượng ổ cứng để lưu trữ index — tăng tốc độ đọc vs giảm tốc độ ghi</v>
+        <v>Giúp bảo mật dữ liệu tuyệt đối trước hacker; nhưng làm tăng giá tiền mua bản quyền phần mềm cơ sở dữ liệu — bảo mật vs chi phí</v>
       </c>
       <c r="F17" t="str">
-        <v>Giúp bảo mật dữ liệu tuyệt đối trước hacker; nhưng làm tăng giá tiền mua bản quyền phần mềm cơ sở dữ liệu — bảo mật vs chi phí</v>
+        <v>Giúp loại bỏ hoàn toàn việc phải viết các câu lệnh JOIN phức tạp giữa các bảng liên kết — loại bỏ JOIN</v>
       </c>
       <c r="G17" t="str">
         <v>Giúp tự động sửa các lỗi chính tả trong bảng; nhưng giới hạn số lượng cột tối đa của bảng dưới 10 cột — sửa chính tả vs giới hạn cột</v>
       </c>
       <c r="H17" t="str">
-        <v>Giúp loại bỏ hoàn toàn việc phải viết các câu lệnh JOIN phức tạp giữa các bảng liên kết — loại bỏ JOIN</v>
+        <v>Giúp tăng tốc độ truy vấn đọc dữ liệu (SELECT) cực nhanh; nhưng làm chậm tốc độ ghi dữ liệu (INSERT/UPDATE/DELETE) và tiêu tốn dung lượng ổ cứng để lưu trữ index — tăng tốc độ đọc vs giảm tốc độ ghi</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -917,19 +917,19 @@
         <v>Memory Leak thường do lỗi lập trình (quên đóng kết nối, quên giải phóng con trỏ). Lỗi này chỉ có thể phát hiện hiệu quả thông qua việc chạy Soak testing (Endurance testing) trong thời gian dài để quan sát đồ thị RAM tiêu thụ đi lên tuyến tính.</v>
       </c>
       <c r="E18" t="str">
+        <v>Hệ thống tự động nén kích thước của các tệp tin lưu trữ để giải phóng không gian ổ cứng — tự động nén giải phóng ổ cứng</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Lập trình viên quên không lắp card màn hình vào bo mạch chủ của máy tính chạy phần mềm — thiếu card màn hình</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Dữ liệu trong bộ nhớ RAM bị hacker lấy trộm và công bố công khai ra internet — rò rỉ dữ liệu</v>
+      </c>
+      <c r="H18" t="str">
         <v>Ứng dụng chiếm dụng bộ nhớ RAM nhưng không giải phóng sau khi sử dụng xong, làm dung lượng RAM trống giảm dần theo thời gian dẫn đến sập hệ thống — rò rỉ RAM gây sập máy chủ</v>
       </c>
-      <c r="F18" t="str">
-        <v>Dữ liệu trong bộ nhớ RAM bị hacker lấy trộm và công bố công khai ra internet — rò rỉ dữ liệu</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Hệ thống tự động nén kích thước của các tệp tin lưu trữ để giải phóng không gian ổ cứng — tự động nén giải phóng ổ cứng</v>
-      </c>
-      <c r="H18" t="str">
-        <v>Lập trình viên quên không lắp card màn hình vào bo mạch chủ của máy tính chạy phần mềm — thiếu card màn hình</v>
-      </c>
       <c r="I18">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -946,19 +946,19 @@
         <v>Nếu không có Timers, các virtual users của JMeter sẽ gửi request liên tiếp ngay khi nhận được response (tốc độ của robot). Điều này tạo ra mức tải cực kỳ khốc liệt và phi thực tế. Chèn Timers (Think Time) giúp mô phỏng chính xác nhịp điệu tương tác của con người (đọc trang mất 3-5s rồi mới click), giúp kết quả đo lường tải sát với thực tế vận hành.</v>
       </c>
       <c r="E19" t="str">
-        <v>Sử dụng các bộ tạo thời gian trễ (Timers - như Uniform Random Timer hoặc Constant Timer) chèn vào giữa các Samplers để giả lập thời gian nghỉ ngẫu nhiên của người dùng — sử dụng JMeter Timers giả lập Think Time</v>
+        <v>Yêu cầu lập trình viên Frontend lập trình cho trang web tự động tải chậm đi 5 giây đối với tất cả các click chuột — làm chậm trang web</v>
       </c>
       <c r="F19" t="str">
-        <v>Yêu cầu lập trình viên Frontend lập trình cho trang web tự động tải chậm đi 5 giây đối với tất cả các click chuột — làm chậm trang web</v>
+        <v>Cấu hình cho máy chạy test tự động tắt kết nối mạng internet trong vòng 3 giây sau mỗi click chuột — ngắt kết nối mạng</v>
       </c>
       <c r="G19" t="str">
         <v>Chỉ chạy bộ kịch bản test hiệu năng với duy nhất 1 người dùng ảo trong toàn bộ phiên chạy — chạy đơn người dùng</v>
       </c>
       <c r="H19" t="str">
-        <v>Cấu hình cho máy chạy test tự động tắt kết nối mạng internet trong vòng 3 giây sau mỗi click chuột — ngắt kết nối mạng</v>
+        <v>Sử dụng các bộ tạo thời gian trễ (Timers - như Uniform Random Timer hoặc Constant Timer) chèn vào giữa các Samplers để giả lập thời gian nghỉ ngẫu nhiên của người dùng — sử dụng JMeter Timers giả lập Think Time</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -978,13 +978,13 @@
         <v>Điểm mà tại đó số lượng người dùng (VUs) tiếp tục tăng nhưng thông lượng (Throughput) đi ngang hoặc giảm, đồng thời thời gian phản hồi (Response Time) bắt đầu tăng vọt tuyến tính; biểu thị giới hạn chịu tải tối đa của hệ thống — bão hòa thông lượng tăng vọt phản hồi</v>
       </c>
       <c r="F20" t="str">
-        <v>Điểm mà tại đó dung lượng ổ cứng vật lý của máy chủ cơ sở dữ liệu bị đầy 100% — đầy ổ cứng</v>
+        <v>Điểm mà tại đó lập trình viên hoàn thành việc viết code 100% các tính năng nghiệp vụ — hoàn thành code</v>
       </c>
       <c r="G20" t="str">
         <v>Điểm mà tại đó số lượng lỗi (Bugs) được phát hiện trong ngày bằng đúng số lượng bug được sửa — bão hòa lỗi</v>
       </c>
       <c r="H20" t="str">
-        <v>Điểm mà tại đó lập trình viên hoàn thành việc viết code 100% các tính năng nghiệp vụ — hoàn thành code</v>
+        <v>Điểm mà tại đó dung lượng ổ cứng vật lý của máy chủ cơ sở dữ liệu bị đầy 100% — đầy ổ cứng</v>
       </c>
       <c r="I20">
         <v>1</v>
@@ -1004,19 +1004,19 @@
         <v>`EXPLAIN` là công cụ đắc lực của DBA/Tester để tuning hiệu năng. Nó chỉ ra database engine sẽ chạy thế nào: Quét tuần tự toàn bộ bảng (Seq Scan - cực chậm trên bảng lớn) hay Quét chỉ mục (Index Scan - cực nhanh). Nhờ đó, QA biết được cần tạo index ở cột nào hoặc viết lại câu lệnh JOIN.</v>
       </c>
       <c r="E21" t="str">
-        <v>Hiển thị kế hoạch thực thi truy vấn (Query Execution Plan) của công cụ tối ưu hóa, chỉ ra các bước quét toàn bảng (Table Scan/Seq Scan) do thiếu Index hoặc thực hiện phép JOIN không tối ưu — hiển thị kế hoạch thực thi định vị quét bảng</v>
+        <v>Tự động chia tách bảng dữ liệu lớn ra thành 10 bảng nhỏ độc lập trên ổ cứng — tự động chia tách bảng</v>
       </c>
       <c r="F21" t="str">
         <v>Tự động sửa chữa các lỗi cú pháp viết sai chính tả của câu lệnh SQL đó — tự sửa lỗi SQL</v>
       </c>
       <c r="G21" t="str">
+        <v>Hiển thị kế hoạch thực thi truy vấn (Query Execution Plan) của công cụ tối ưu hóa, chỉ ra các bước quét toàn bảng (Table Scan/Seq Scan) do thiếu Index hoặc thực hiện phép JOIN không tối ưu — hiển thị kế hoạch thực thi định vị quét bảng</v>
+      </c>
+      <c r="H21" t="str">
         <v>Mã hóa toàn bộ các bản ghi kết quả trả về của câu lệnh SQL đó để bảo mật thông tin tài chính — mã hóa kết quả SQL</v>
       </c>
-      <c r="H21" t="str">
-        <v>Tự động chia tách bảng dữ liệu lớn ra thành 10 bảng nhỏ độc lập trên ổ cứng — tự động chia tách bảng</v>
-      </c>
       <c r="I21">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1033,19 +1033,19 @@
         <v>Hệ thống có cache chạy rất nhanh (Response Time &lt; 10ms) vì không phải truy vấn DB. Nhưng nếu cache bị hết hạn đồng loạt (Cache Stampede), hàng nghìn requests sẽ chọc thẳng xuống DB cùng lúc, dễ làm sập DB. Kịch bản test sập cache giúp đánh giá khả năng phòng vệ của DB (như cơ chế mutex lock, rate limiting).</v>
       </c>
       <c r="E22" t="str">
+        <v>Chỉ chạy test hiệu năng khi hệ thống Redis Cache hoạt động ổn định và không bao giờ được phép tắt cache — test khi có cache ổn định</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Tăng dung lượng bộ nhớ RAM của máy chủ chứa Redis Cache lên gấp 100 lần để đảm bảo không bao giờ hết hạn — nâng cấp RAM cực đoan</v>
+      </c>
+      <c r="G22" t="str">
         <v>Thiết kế kịch bản kiểm thử tải đột biến (Spike test) đồng thời xóa sạch cache (Flush cache) để ép toàn bộ các yêu cầu của người dùng chọc thẳng xuống cơ sở dữ liệu chính (DB), đo lường khả năng chịu tải của DB — giả lập sập cache đo lường sức chịu tải DB</v>
       </c>
-      <c r="F22" t="str">
-        <v>Chỉ chạy test hiệu năng khi hệ thống Redis Cache hoạt động ổn định và không bao giờ được phép tắt cache — test khi có cache ổn định</v>
-      </c>
-      <c r="G22" t="str">
+      <c r="H22" t="str">
         <v>Yêu cầu lập trình viên viết code xóa bỏ hoàn toàn cơ chế lưu bộ nhớ đệm để hệ thống chạy đơn giản hơn — loại bỏ cache</v>
       </c>
-      <c r="H22" t="str">
-        <v>Tăng dung lượng bộ nhớ RAM của máy chủ chứa Redis Cache lên gấp 100 lần để đảm bảo không bao giờ hết hạn — nâng cấp RAM cực đoan</v>
-      </c>
       <c r="I22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1062,19 +1062,19 @@
         <v>Thiết kế sai mô hình tải sẽ cho kết quả test vô giá trị. Với website E-commerce public, người dùng truy cập ngẫu nhiên (Open model). Nếu server bị chậm, người dùng mới vẫn tiếp tục vào tạo request mới, làm hàng đợi phình to và sập server nhanh hơn. Closed model (như trong JMeter mặc định dùng thread group truyền thống) giới hạn số VUs cố định, nếu server chậm thì robot cũng gửi request chậm lại, làm giảm tải ảo lên server.</v>
       </c>
       <c r="E23" t="str">
+        <v>Closed chạy nhanh hơn Open gấp 10 lần do không tốn tài nguyên giả lập tải — so sánh hiệu năng tốc độ</v>
+      </c>
+      <c r="F23" t="str">
         <v>Closed: Số lượng người dùng hoạt động cố định, request mới chỉ gửi sau khi nhận response cũ (thích hợp hệ thống nội bộ ERP); Open: Request mới gửi đến theo phân phối ngẫu nhiên (như Poisson) bất kể người dùng trước đã nhận response chưa (thích hợp Web bán lẻ/E-commerce public) — Closed người dùng cố định vs Open request ngẫu nhiên liên tục</v>
       </c>
-      <c r="F23" t="str">
+      <c r="G23" t="str">
         <v>Closed chỉ áp dụng cho kiểm thử tự động; Open chỉ áp dụng cho kiểm thử thủ công — phân loại phương pháp test</v>
       </c>
-      <c r="G23" t="str">
+      <c r="H23" t="str">
         <v>Closed bắt buộc phải đóng toàn bộ các cổng kết nối mạng; Open yêu cầu mở toàn bộ cổng mạng — cơ chế bảo mật cổng mạng</v>
       </c>
-      <c r="H23" t="str">
-        <v>Closed chạy nhanh hơn Open gấp 10 lần do không tốn tài nguyên giả lập tải — so sánh hiệu năng tốc độ</v>
-      </c>
       <c r="I23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1094,10 +1094,10 @@
         <v>Làm tăng vọt thời gian phản hồi (Response Time) và gây lỗi treo cứng (Deadlock); QA thiết kế kịch bản test song song (Concurrency test) cho hàng trăm người dùng ảo cùng thực hiện cập nhật số dư của đúng một tài khoản ngân hàng cùng một lúc — test song song đồng thời phát hiện tranh chấp khóa</v>
       </c>
       <c r="F24" t="str">
+        <v>Làm cho hệ thống tự động đổi kiểu dữ liệu của cột khóa ngoại từ int sang string; QA chạy test kiểm tra kiểu dữ liệu — thay đổi kiểu dữ liệu</v>
+      </c>
+      <c r="G24" t="str">
         <v>Làm tăng dung lượng file sao lưu database lên gấp đôi; QA thiết kế kịch bản sao lưu dữ liệu hàng ngày — ảnh hưởng sao lưu</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Làm cho hệ thống tự động đổi kiểu dữ liệu của cột khóa ngoại từ int sang string; QA chạy test kiểm tra kiểu dữ liệu — thay đổi kiểu dữ liệu</v>
       </c>
       <c r="H24" t="str">
         <v>Lập tức làm sập nguồn điện của toàn bộ hệ thống máy chủ vật lý chứa database; QA diễn tập mất điện — sập nguồn máy chủ</v>
@@ -1120,19 +1120,19 @@
         <v>Một máy tính cá nhân (JMeter Master) thường chỉ giả lập được tối đa 1,000 - 2,000 VUs tùy thuộc vào độ phức tạp của script. Để giả lập 50k VUs, ta phải dùng mô hình phân tán (Distributed), dùng nhiều máy Slave (Injectors) bơm tải đồng loạt. Sự đồng bộ thời gian (NTP clock sync) và băng thông mạng không bị nghẽn giữa Master-Slave là chìa khóa để thu thập dữ liệu tải chính xác.</v>
       </c>
       <c r="E25" t="str">
+        <v>Yêu cầu tất cả các máy Slave bắt buộc phải chạy hệ điều hành macOS phiên bản mới nhất — yêu cầu hệ điều hành Slave</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Đảm bảo rằng máy Master tự động tắt nguồn điện của tất cả các máy Slave ngay khi chạy test xong — tắt nguồn máy Slave</v>
+      </c>
+      <c r="G25" t="str">
         <v>Thiết lập 1 máy Master điều phối và nhiều máy Slave trực tiếp bơm tải để tránh quá tải CPU/băng thông mạng của máy Master; lưu ý quan trọng nhất là các máy Slave phải nằm trong cùng mạng LAN hoặc kết nối mạng có độ trễ cực thấp và không bị chặn tường lửa các port điều khiển — Master-Slave phân tán tải và đồng bộ mạng LAN</v>
       </c>
-      <c r="F25" t="str">
+      <c r="H25" t="str">
         <v>Thiết lập để các máy Slave tự động mã hóa dữ liệu chạy test bằng thuật toán bảo mật MD5 trước khi gửi về Master — mã hóa dữ liệu truyền</v>
       </c>
-      <c r="G25" t="str">
-        <v>Yêu cầu tất cả các máy Slave bắt buộc phải chạy hệ điều hành macOS phiên bản mới nhất — yêu cầu hệ điều hành Slave</v>
-      </c>
-      <c r="H25" t="str">
-        <v>Đảm bảo rằng máy Master tự động tắt nguồn điện của tất cả các máy Slave ngay khi chạy test xong — tắt nguồn máy Slave</v>
-      </c>
       <c r="I25">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1149,19 +1149,19 @@
         <v>Hệ thống bất đồng bộ trả về HTTP 202 Accepted ngay khi nhận tin nhắn vào queue (Response Time &lt; 5ms). Tuy nhiên, tin nhắn có thể mất 10s xếp hàng và xử lý ở phía sau. Sử dụng Correlation ID kết hợp công cụ Distributed Tracing (như Jaeger, Zipkin) hoặc quét DB/log đối chiếu timestamp là cách duy nhất để đo lường chính xác thời gian xử lý thực tế của nghiệp vụ (End-to-End Processing Time).</v>
       </c>
       <c r="E26" t="str">
+        <v>Chỉ đo thời gian từ lúc gửi tin nhắn vào queue cho đến khi nhận được xác nhận thành công (ACK) của hàng đợi — chỉ đo thời gian gửi queue</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Yêu cầu lập trình viên tạm thời chuyển toàn bộ kiến trúc bất đồng bộ sang kiến trúc gọi API đồng bộ để dễ dàng đo lường — chuyển sang đồng bộ</v>
+      </c>
+      <c r="G26" t="str">
         <v>Sử dụng mã định danh giao dịch duy nhất (Correlation ID) đính kèm vào tin nhắn, ghi lại timestamp tại thời điểm bắt đầu gửi vào queue và timestamp tại thời điểm service cuối cùng xử lý xong lưu trong database/log, sau đó đối chiếu chênh lệch — theo dõi Correlation ID và đối chiếu timestamp</v>
-      </c>
-      <c r="F26" t="str">
-        <v>Chỉ đo thời gian từ lúc gửi tin nhắn vào queue cho đến khi nhận được xác nhận thành công (ACK) của hàng đợi — chỉ đo thời gian gửi queue</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Yêu cầu lập trình viên tạm thời chuyển toàn bộ kiến trúc bất đồng bộ sang kiến trúc gọi API đồng bộ để dễ dàng đo lường — chuyển sang đồng bộ</v>
       </c>
       <c r="H26" t="str">
         <v>Chạy thử nghiệm kịch bản test hiệu năng thủ công bằng cách sử dụng đồng hồ bấm giờ trên tay để đo — đo thủ công bấm giờ</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
